--- a/artfynd/A 17849-2023 artfynd.xlsx
+++ b/artfynd/A 17849-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17849-2023 artfynd.xlsx
+++ b/artfynd/A 17849-2023 artfynd.xlsx
@@ -819,7 +819,7 @@
         <v>119973164</v>
       </c>
       <c r="B3" t="n">
-        <v>56233</v>
+        <v>56243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 17849-2023 artfynd.xlsx
+++ b/artfynd/A 17849-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2207953</v>
+        <v>119973164</v>
       </c>
       <c r="B2" t="n">
-        <v>104489</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219686</v>
+        <v>100053</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Erinaceus europaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,29 +708,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rödeby Sofielund V hundklubben, Bl</t>
+          <t>Västergården, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538834.5268134557</v>
+        <v>538877</v>
       </c>
       <c r="R2" t="n">
-        <v>6233520.301926045</v>
+        <v>6233433</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,27 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-04-17</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-04-17</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ravinslänt</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,62 +776,51 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bokskog</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kjell Pettersson</t>
+          <t>Johan Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kjell Pettersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Via Johan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119973164</v>
+        <v>2207953</v>
       </c>
       <c r="B3" t="n">
-        <v>56243</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100053</v>
+        <v>219686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Erinaceus europaeus</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,24 +828,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västergården, Bl</t>
+          <t>Rödeby Sofielund V hundklubben, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538877</v>
+        <v>538835</v>
       </c>
       <c r="R3" t="n">
-        <v>6233433</v>
+        <v>6233520</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,22 +874,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2010-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2010-04-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ravinslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,22 +896,28 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bokskog</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Nilsson</t>
+          <t>Kjell Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Nilsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>WWF - Tillsammans för Sveriges igelkottar</t>
-        </is>
-      </c>
+          <t>Kjell Pettersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17849-2023 artfynd.xlsx
+++ b/artfynd/A 17849-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119973164</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,8 +928,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2207953</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>